--- a/rnd/templates/glossary_template.xlsx
+++ b/rnd/templates/glossary_template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,18 +28,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000056A7"/>
       <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -55,7 +48,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -63,33 +56,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D0D7DE"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D0D7DE"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D0D7DE"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D0D7DE"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -456,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -465,100 +440,134 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DataHive Glossary Template</t>
-        </is>
-      </c>
+          <t>DataHive Glossary — multi-connector</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>How to use</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Use the Glossary sheet. One row = one column on any connected platform.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1. Download this template from the Glossary tab.</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2. Fill one row per column you want to document.</t>
+          <t>Identifiers</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3. Keep the header names exactly as provided (order can vary).</t>
+          <t xml:space="preserve">  connection  — saved Connectors display name (recommended). Use postgres / blank for local Postgres.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4. Upload the file back from the Glossary tab — any file name is fine.</t>
+          <t xml:space="preserve">  platform    — optional: aws, azure, gcp, snowflake, postgres (helps when connection is new).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  database    — database / catalog / project id (BigQuery project, Snowflake DB, Glue DB, etc.).</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Identifier columns (required to locate the asset column):</t>
+          <t xml:space="preserve">  schema      — schema / dataset / namespace.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  connection, database, schema, table, column</t>
+          <t xml:space="preserve">  table       — table / view / object name.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  column      — column / field name.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Metadata columns written into the column comment / Assets metadata:</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  business_name, description, business_definition, classification,</t>
+          <t>Metadata</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t xml:space="preserve">  business_name, description, business_definition, classification,</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t xml:space="preserve">  sensitivity, source_system, owner, steward</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-    </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>On upload, DataHive updates PostgreSQL COMMENT ON COLUMN for each matching</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>database.schema.table.column. Assets structure view shows the metadata immediately.</t>
+          <t>Behavior on upload</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Every row is upserted into MongoDB asset_glossary (shared registry).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Rows resolved to Postgres also sync COMMENT ON COLUMN for Assets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • AWS / Azure / GCP / Snowflake rows use the same registry path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Tip: create the connector first under Connectors, then set connection to its display name.</t>
         </is>
       </c>
     </row>
@@ -573,155 +582,454 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>connection</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>database</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>schema</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>table</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>column</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>business_name</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>business_definition</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>classification</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>sensitivity</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>source_system</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>owner</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>steward</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Local Postgres</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>datahivepoc</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>dhpoc-bronze</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>test_customer_tbl</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>customer_nm</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Customer name</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Legal or preferred customer name</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Canonical party name used across billing and care</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>PII</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>confidential</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>data-steward</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>governance</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AWS Prod</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>aws</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>analytics</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>customers</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Customer email</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Primary contact email</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Used for notifications and identity matching</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PII</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>restricted</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>platform-owner</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Azure Analytics</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>azure</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>synapse</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>dbo</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>FactUsage</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>customer_id</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Customer ID</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Customer identification number assigned by the organization.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>Unique identifier assigned to every Customer.</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>PII</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>Confidential</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>Workday</t>
-        </is>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="M2" s="4" t="inlineStr">
-        <is>
-          <t>Sales Data Steward</t>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Surrogate customer key</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Joins usage facts to customer dimension</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bi-owner</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>data-steward</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GCP Marketing</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>gcp</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>acme-dw</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>dh_customer</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>customer_id</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Customer ID</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Business customer key</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Hub key for customer 360</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>analytics-owner</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>steward</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Snowflake Finance</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>snowflake</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>GOLD</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AR_AGING</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>INVOICE_ID</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Invoice ID</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Billing invoice identifier</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Links payments and AR aging</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>finance-owner</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>steward</t>
         </is>
       </c>
     </row>

--- a/rnd/templates/glossary_template.xlsx
+++ b/rnd/templates/glossary_template.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -444,9 +444,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -454,9 +452,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -506,9 +502,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -530,9 +524,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -561,9 +553,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
@@ -571,6 +561,14 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
